--- a/data/trans_orig/P6604-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6604-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>177338</t>
+          <t>177597</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>216251</t>
+          <t>216898</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>129297</t>
+          <t>129274</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>157999</t>
+          <t>158867</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>316203</t>
+          <t>316526</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>363842</t>
+          <t>363076</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,16%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>78032</t>
+          <t>75784</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>111721</t>
+          <t>112045</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35657</t>
+          <t>35165</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59262</t>
+          <t>58943</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>119609</t>
+          <t>120778</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>161703</t>
+          <t>162413</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,25%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34028</t>
+          <t>33625</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>58225</t>
+          <t>58329</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>7905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22870</t>
+          <t>22244</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>45421</t>
+          <t>45137</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>76737</t>
+          <t>74625</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14834</t>
+          <t>13850</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32797</t>
+          <t>32715</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6295</t>
+          <t>6040</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20696</t>
+          <t>20102</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24505</t>
+          <t>24080</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48718</t>
+          <t>47959</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>144960</t>
+          <t>144568</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>178311</t>
+          <t>177038</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>139464</t>
+          <t>142444</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>169353</t>
+          <t>169450</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>295297</t>
+          <t>296725</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>339454</t>
+          <t>339642</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,56%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>49286</t>
+          <t>47433</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77946</t>
+          <t>77717</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33905</t>
+          <t>33156</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57855</t>
+          <t>57061</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89068</t>
+          <t>88377</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125675</t>
+          <t>126016</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24954</t>
+          <t>26103</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47105</t>
+          <t>48111</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16949</t>
+          <t>17097</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34177</t>
+          <t>35222</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>46215</t>
+          <t>47094</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>75643</t>
+          <t>75336</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20510</t>
+          <t>19130</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13588</t>
+          <t>13023</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10953</t>
+          <t>10694</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28480</t>
+          <t>28063</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>55369</t>
+          <t>55220</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>87559</t>
+          <t>86429</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15544</t>
+          <t>15547</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30345</t>
+          <t>30275</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>77124</t>
+          <t>76891</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>112222</t>
+          <t>111295</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93114</t>
+          <t>93434</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>129901</t>
+          <t>128985</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12608</t>
+          <t>13013</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26372</t>
+          <t>26990</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>112264</t>
+          <t>112182</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>152156</t>
+          <t>151362</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,5%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>92302</t>
+          <t>90396</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>129632</t>
+          <t>127302</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>5509</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17191</t>
+          <t>17262</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>100525</t>
+          <t>101697</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>139540</t>
+          <t>139190</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73749</t>
+          <t>73248</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>108886</t>
+          <t>108447</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11894</t>
+          <t>11984</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>76097</t>
+          <t>78500</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>113697</t>
+          <t>112477</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>148690</t>
+          <t>147654</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>196718</t>
+          <t>197309</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>120356</t>
+          <t>121700</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>154364</t>
+          <t>153464</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>282621</t>
+          <t>281962</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>341786</t>
+          <t>340548</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>152995</t>
+          <t>154045</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>201295</t>
+          <t>202224</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>75921</t>
+          <t>74352</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>107702</t>
+          <t>107983</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>235027</t>
+          <t>236628</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>293253</t>
+          <t>294310</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>180394</t>
+          <t>176743</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>229565</t>
+          <t>226345</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>41300</t>
+          <t>39946</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>68064</t>
+          <t>67222</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>231614</t>
+          <t>229163</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>285205</t>
+          <t>286599</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,31%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>130166</t>
+          <t>131737</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>176147</t>
+          <t>176643</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>17238</t>
+          <t>16526</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38271</t>
+          <t>37325</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>155908</t>
+          <t>155690</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>208065</t>
+          <t>206346</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27875</t>
+          <t>28116</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>50458</t>
+          <t>51197</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>42695</t>
+          <t>43045</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>70472</t>
+          <t>69823</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>77653</t>
+          <t>77152</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>112799</t>
+          <t>112612</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23819</t>
+          <t>23520</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44940</t>
+          <t>45071</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33296</t>
+          <t>32742</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59235</t>
+          <t>57398</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>62900</t>
+          <t>62012</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>95710</t>
+          <t>94844</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,99%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>38281</t>
+          <t>38437</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>63256</t>
+          <t>61648</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>42070</t>
+          <t>42887</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>69186</t>
+          <t>69366</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>87498</t>
+          <t>88280</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>123356</t>
+          <t>124033</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,37%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>49476</t>
+          <t>49989</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>77184</t>
+          <t>77124</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>43538</t>
+          <t>42739</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>69653</t>
+          <t>68340</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>96877</t>
+          <t>98941</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>135983</t>
+          <t>138074</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,92%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>596761</t>
+          <t>600816</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>682225</t>
+          <t>685871</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>483932</t>
+          <t>481205</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>547522</t>
+          <t>546429</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1101298</t>
+          <t>1103860</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1211867</t>
+          <t>1213327</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,49%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>437137</t>
+          <t>436527</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>514762</t>
+          <t>512515</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>222249</t>
+          <t>218595</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>280601</t>
+          <t>274512</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>672019</t>
+          <t>675071</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>769850</t>
+          <t>771286</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>408458</t>
+          <t>404603</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>479497</t>
+          <t>483241</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>135537</t>
+          <t>135152</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>179670</t>
+          <t>183117</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>557064</t>
+          <t>556656</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>647176</t>
+          <t>645629</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>306435</t>
+          <t>305527</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>374738</t>
+          <t>370391</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>85746</t>
+          <t>85399</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>127083</t>
+          <t>127055</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>405903</t>
+          <t>404597</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>483714</t>
+          <t>484298</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>128006</t>
+          <t>129116</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>163939</t>
+          <t>163847</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82896</t>
+          <t>83049</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>111804</t>
+          <t>112546</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>221636</t>
+          <t>222726</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>266701</t>
+          <t>266020</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,7%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71569</t>
+          <t>71978</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104651</t>
+          <t>103760</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50229</t>
+          <t>51291</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77770</t>
+          <t>77575</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>130456</t>
+          <t>128601</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>173579</t>
+          <t>170028</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40430</t>
+          <t>40740</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68979</t>
+          <t>68852</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11906</t>
+          <t>11811</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30303</t>
+          <t>29466</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>56509</t>
+          <t>57870</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>89629</t>
+          <t>90247</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -4719,12 +4719,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9272</t>
+          <t>9103</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27435</t>
+          <t>27516</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4734,12 +4734,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6679</t>
+          <t>6174</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20602</t>
+          <t>19519</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4769,12 +4769,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18966</t>
+          <t>18526</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41492</t>
+          <t>41165</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4804,12 +4804,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -4949,12 +4949,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>94329</t>
+          <t>93659</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>129857</t>
+          <t>128331</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>77065</t>
+          <t>75481</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>103978</t>
+          <t>102449</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4999,12 +4999,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>179846</t>
+          <t>178213</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>223527</t>
+          <t>223023</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,77%</t>
         </is>
       </c>
     </row>
@@ -5062,12 +5062,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75547</t>
+          <t>75063</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>108374</t>
+          <t>108502</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5077,12 +5077,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44433</t>
+          <t>44364</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70171</t>
+          <t>70581</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5112,12 +5112,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>129332</t>
+          <t>129306</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170329</t>
+          <t>172846</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,9%</t>
         </is>
       </c>
     </row>
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32864</t>
+          <t>33815</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60894</t>
+          <t>61596</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6556</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20331</t>
+          <t>19786</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5225,12 +5225,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44003</t>
+          <t>43525</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73724</t>
+          <t>73197</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -5288,12 +5288,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15195</t>
+          <t>15443</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5303,12 +5303,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14935</t>
+          <t>14751</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8032</t>
+          <t>8004</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24736</t>
+          <t>24637</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -5518,12 +5518,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57581</t>
+          <t>57403</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>85799</t>
+          <t>85985</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5533,12 +5533,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23245</t>
+          <t>23469</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>41978</t>
+          <t>42123</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>85555</t>
+          <t>85858</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>120150</t>
+          <t>121160</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5603,12 +5603,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,96%</t>
         </is>
       </c>
     </row>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>88164</t>
+          <t>88588</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>121069</t>
+          <t>119488</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34785</t>
+          <t>35664</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>56085</t>
+          <t>55446</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>127699</t>
+          <t>129734</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>168322</t>
+          <t>169386</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>43,28%</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>63073</t>
+          <t>64219</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92668</t>
+          <t>93442</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14828</t>
+          <t>15210</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32371</t>
+          <t>33406</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5794,12 +5794,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82361</t>
+          <t>84553</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>120036</t>
+          <t>119473</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5829,12 +5829,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18233</t>
+          <t>18295</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40909</t>
+          <t>39211</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5872,12 +5872,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20105</t>
+          <t>19263</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28343</t>
+          <t>28170</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52779</t>
+          <t>52801</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>89553</t>
+          <t>90791</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>129092</t>
+          <t>129313</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6102,12 +6102,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>79926</t>
+          <t>79651</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112752</t>
+          <t>111294</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6137,12 +6137,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6157,12 +6157,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>179793</t>
+          <t>181543</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>232922</t>
+          <t>228148</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6172,12 +6172,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>31,61%</t>
         </is>
       </c>
     </row>
@@ -6200,12 +6200,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>130426</t>
+          <t>129494</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>170957</t>
+          <t>169748</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>90294</t>
+          <t>89469</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>122928</t>
+          <t>123371</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>227569</t>
+          <t>229695</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>281678</t>
+          <t>282040</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,08%</t>
         </is>
       </c>
     </row>
@@ -6313,12 +6313,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>88637</t>
+          <t>87742</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>124085</t>
+          <t>122489</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6328,12 +6328,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6348,12 +6348,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>52747</t>
+          <t>52410</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>83685</t>
+          <t>81956</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6363,12 +6363,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6383,12 +6383,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>149069</t>
+          <t>150633</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>193964</t>
+          <t>200420</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46507</t>
+          <t>47170</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>75344</t>
+          <t>74896</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20702</t>
+          <t>20091</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40982</t>
+          <t>41741</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74169</t>
+          <t>72707</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>110252</t>
+          <t>108023</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,97%</t>
         </is>
       </c>
     </row>
@@ -6656,12 +6656,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7896</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22570</t>
+          <t>23268</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6671,12 +6671,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>23798</t>
+          <t>23394</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>44952</t>
+          <t>44484</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>35425</t>
+          <t>36310</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>61223</t>
+          <t>61731</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,79%</t>
         </is>
       </c>
     </row>
@@ -6769,12 +6769,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20442</t>
+          <t>20073</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39779</t>
+          <t>39361</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>51855</t>
+          <t>53352</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>78390</t>
+          <t>78852</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>79357</t>
+          <t>78759</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>112807</t>
+          <t>113904</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,67%</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>46744</t>
+          <t>48156</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>73612</t>
+          <t>73318</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40283</t>
+          <t>39639</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>65550</t>
+          <t>66243</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>94736</t>
+          <t>97009</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>130590</t>
+          <t>131107</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,91%</t>
         </is>
       </c>
     </row>
@@ -6995,12 +6995,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>37881</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>61357</t>
+          <t>62348</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7010,12 +7010,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>16654</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>36336</t>
+          <t>37251</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>59766</t>
+          <t>59014</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>89608</t>
+          <t>90272</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>415026</t>
+          <t>420175</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>489560</t>
+          <t>491943</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>316986</t>
+          <t>317144</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>381273</t>
+          <t>377751</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>755882</t>
+          <t>754551</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>849398</t>
+          <t>848554</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,96%</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>426619</t>
+          <t>424875</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>498239</t>
+          <t>496273</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7353,12 +7353,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>307849</t>
+          <t>307863</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>369425</t>
+          <t>369900</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>752289</t>
+          <t>746669</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>845115</t>
+          <t>846700</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,88%</t>
         </is>
       </c>
     </row>
@@ -7451,12 +7451,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>307993</t>
+          <t>309045</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>375945</t>
+          <t>377511</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7466,12 +7466,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>148483</t>
+          <t>148223</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>199067</t>
+          <t>198081</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7521,12 +7521,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>473065</t>
+          <t>472467</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>557290</t>
+          <t>555166</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -7564,12 +7564,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>134955</t>
+          <t>137626</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>186337</t>
+          <t>189932</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>71251</t>
+          <t>70067</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>106106</t>
+          <t>104676</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>216903</t>
+          <t>217612</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>278223</t>
+          <t>278442</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -8027,12 +8027,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>130710</t>
+          <t>130672</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>165307</t>
+          <t>164358</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>96718</t>
+          <t>95652</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>125850</t>
+          <t>125090</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>235472</t>
+          <t>237915</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>283070</t>
+          <t>280735</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,11%</t>
         </is>
       </c>
     </row>
@@ -8140,12 +8140,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71024</t>
+          <t>71950</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>103302</t>
+          <t>105384</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52745</t>
+          <t>51402</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78532</t>
+          <t>78670</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>132478</t>
+          <t>131495</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>174368</t>
+          <t>172920</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,18%</t>
         </is>
       </c>
     </row>
@@ -8253,12 +8253,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17843</t>
+          <t>18070</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39652</t>
+          <t>38162</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8268,12 +8268,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18838</t>
+          <t>20242</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39382</t>
+          <t>39695</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8303,12 +8303,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44133</t>
+          <t>41540</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71547</t>
+          <t>70837</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8338,12 +8338,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -8366,12 +8366,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>7313</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23348</t>
+          <t>23455</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8381,12 +8381,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8401,12 +8401,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18266</t>
+          <t>20032</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8416,12 +8416,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15535</t>
+          <t>15742</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35107</t>
+          <t>35336</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8451,12 +8451,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -8596,12 +8596,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92157</t>
+          <t>92649</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>125262</t>
+          <t>124934</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>94138</t>
+          <t>94556</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>121083</t>
+          <t>122493</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>195146</t>
+          <t>195291</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>237933</t>
+          <t>237225</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8681,12 +8681,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>54,99%</t>
         </is>
       </c>
     </row>
@@ -8709,12 +8709,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66006</t>
+          <t>67111</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>95721</t>
+          <t>96659</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40308</t>
+          <t>39442</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65302</t>
+          <t>65686</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>112773</t>
+          <t>111540</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>151775</t>
+          <t>151008</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,0%</t>
         </is>
       </c>
     </row>
@@ -8822,12 +8822,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27838</t>
+          <t>28099</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53753</t>
+          <t>52152</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15053</t>
+          <t>15510</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32894</t>
+          <t>33300</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8872,12 +8872,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47742</t>
+          <t>49617</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>78311</t>
+          <t>82552</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8907,12 +8907,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>19,14%</t>
         </is>
       </c>
     </row>
@@ -8935,12 +8935,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>8307</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23854</t>
+          <t>23748</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8950,12 +8950,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2152</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12407</t>
+          <t>11940</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8985,12 +8985,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12275</t>
+          <t>13684</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>30018</t>
+          <t>31388</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9020,12 +9020,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -9165,12 +9165,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31009</t>
+          <t>31657</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54413</t>
+          <t>55428</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9180,12 +9180,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14175</t>
+          <t>14580</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29323</t>
+          <t>29686</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48764</t>
+          <t>49760</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>78093</t>
+          <t>77736</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -9278,12 +9278,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56196</t>
+          <t>55717</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>83628</t>
+          <t>84346</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9293,12 +9293,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14974</t>
+          <t>15127</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28952</t>
+          <t>30171</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9328,12 +9328,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>75152</t>
+          <t>75184</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>107689</t>
+          <t>109378</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9363,12 +9363,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,67%</t>
         </is>
       </c>
     </row>
@@ -9391,12 +9391,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>62229</t>
+          <t>63228</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>91219</t>
+          <t>91909</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12430</t>
+          <t>12064</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27156</t>
+          <t>26582</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>79846</t>
+          <t>79691</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>112411</t>
+          <t>111141</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9476,12 +9476,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,29%</t>
         </is>
       </c>
     </row>
@@ -9504,12 +9504,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17681</t>
+          <t>18422</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37382</t>
+          <t>38663</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11953</t>
+          <t>11326</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9554,12 +9554,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23817</t>
+          <t>23298</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45294</t>
+          <t>44405</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9589,12 +9589,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -9734,12 +9734,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>95849</t>
+          <t>97164</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>132276</t>
+          <t>134355</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9749,12 +9749,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>102384</t>
+          <t>100999</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>138158</t>
+          <t>137970</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9784,12 +9784,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>208941</t>
+          <t>207226</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>261798</t>
+          <t>259463</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9819,12 +9819,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -9847,12 +9847,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>151121</t>
+          <t>150409</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>192371</t>
+          <t>193443</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9862,12 +9862,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>95739</t>
+          <t>93471</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>130420</t>
+          <t>128292</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9897,12 +9897,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>260789</t>
+          <t>260288</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>314320</t>
+          <t>314251</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9932,12 +9932,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,99%</t>
         </is>
       </c>
     </row>
@@ -9960,12 +9960,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>96862</t>
+          <t>96981</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>136823</t>
+          <t>133630</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>65432</t>
+          <t>65082</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>97221</t>
+          <t>97083</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>171162</t>
+          <t>169931</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>219686</t>
+          <t>219840</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,88%</t>
         </is>
       </c>
     </row>
@@ -10073,12 +10073,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>63908</t>
+          <t>65657</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>99126</t>
+          <t>97721</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43104</t>
+          <t>42625</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71849</t>
+          <t>70826</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>114996</t>
+          <t>112791</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>160173</t>
+          <t>157505</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19286</t>
+          <t>18685</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40976</t>
+          <t>39614</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>25878</t>
+          <t>25333</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>49225</t>
+          <t>47604</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>50248</t>
+          <t>50066</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>80308</t>
+          <t>80064</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,5%</t>
         </is>
       </c>
     </row>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38607</t>
+          <t>38528</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>64640</t>
+          <t>64147</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10431,12 +10431,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>54179</t>
+          <t>54716</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>82678</t>
+          <t>80096</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10466,12 +10466,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>98827</t>
+          <t>100501</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>135838</t>
+          <t>135522</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,7%</t>
         </is>
       </c>
     </row>
@@ -10529,12 +10529,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>49524</t>
+          <t>50303</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>75860</t>
+          <t>76810</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10544,12 +10544,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>47581</t>
+          <t>48054</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>73178</t>
+          <t>73029</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10579,12 +10579,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>105416</t>
+          <t>106216</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>141825</t>
+          <t>142957</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,6%</t>
         </is>
       </c>
     </row>
@@ -10642,12 +10642,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>41090</t>
+          <t>39590</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>66001</t>
+          <t>65465</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10657,12 +10657,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10677,12 +10677,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>24081</t>
+          <t>24278</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>45705</t>
+          <t>45492</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10692,12 +10692,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10712,12 +10712,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>69792</t>
+          <t>69740</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>103090</t>
+          <t>103100</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10727,12 +10727,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>405689</t>
+          <t>406415</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>478814</t>
+          <t>478315</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>362091</t>
+          <t>363480</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>427782</t>
+          <t>425121</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>784539</t>
+          <t>788919</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>883556</t>
+          <t>881601</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,04%</t>
         </is>
       </c>
     </row>
@@ -10985,12 +10985,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>425765</t>
+          <t>426945</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>493743</t>
+          <t>497770</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11000,12 +11000,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>286190</t>
+          <t>289808</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>347635</t>
+          <t>347418</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>728812</t>
+          <t>733771</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>825070</t>
+          <t>823267</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11070,12 +11070,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,66%</t>
         </is>
       </c>
     </row>
@@ -11098,12 +11098,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>288646</t>
+          <t>291288</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>356029</t>
+          <t>355038</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11113,12 +11113,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>185952</t>
+          <t>184167</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>237977</t>
+          <t>235085</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11148,12 +11148,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>491806</t>
+          <t>486674</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>577146</t>
+          <t>570081</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11183,12 +11183,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -11211,12 +11211,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>165396</t>
+          <t>166095</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>216262</t>
+          <t>219391</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11226,12 +11226,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>93330</t>
+          <t>91921</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>132677</t>
+          <t>134586</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11261,12 +11261,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>270172</t>
+          <t>268492</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>339727</t>
+          <t>336217</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11296,12 +11296,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -11669,32 +11669,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>108668</t>
+          <t>121448</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>95755</t>
+          <t>105789</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>122699</t>
+          <t>136176</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11704,32 +11704,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>72164</t>
+          <t>77440</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61569</t>
+          <t>67232</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83248</t>
+          <t>88954</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11739,32 +11739,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>180833</t>
+          <t>198888</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>164063</t>
+          <t>180312</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>199512</t>
+          <t>218560</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,55%</t>
         </is>
       </c>
     </row>
@@ -11782,32 +11782,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50778</t>
+          <t>54130</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38550</t>
+          <t>41801</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63786</t>
+          <t>67455</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11817,32 +11817,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50642</t>
+          <t>53752</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40548</t>
+          <t>43838</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61564</t>
+          <t>64576</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11852,32 +11852,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>101420</t>
+          <t>107882</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>83728</t>
+          <t>90834</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116973</t>
+          <t>124471</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>34,48%</t>
         </is>
       </c>
     </row>
@@ -11895,32 +11895,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12602</t>
+          <t>14231</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6611</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21845</t>
+          <t>25127</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11930,32 +11930,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19555</t>
+          <t>21182</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12854</t>
+          <t>14709</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29432</t>
+          <t>30632</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11965,32 +11965,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>32157</t>
+          <t>35413</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22904</t>
+          <t>25688</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>45589</t>
+          <t>48379</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -12008,32 +12008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7809</t>
+          <t>10159</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19027</t>
+          <t>21541</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12043,32 +12043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>8634</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13607</t>
+          <t>14616</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12078,32 +12078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16064</t>
+          <t>18792</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9825</t>
+          <t>11566</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26708</t>
+          <t>30943</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -12121,17 +12121,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>179857</t>
+          <t>199967</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179857</t>
+          <t>199967</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>179857</t>
+          <t>199967</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12156,17 +12156,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>150617</t>
+          <t>161008</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>150617</t>
+          <t>161008</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>150617</t>
+          <t>161008</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12191,17 +12191,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>330474</t>
+          <t>360976</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>330474</t>
+          <t>360976</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>330474</t>
+          <t>360976</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12238,32 +12238,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>90780</t>
+          <t>98082</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>77477</t>
+          <t>83424</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>103396</t>
+          <t>111881</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12273,32 +12273,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>66503</t>
+          <t>72116</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>57009</t>
+          <t>62568</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>75974</t>
+          <t>81868</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -12308,32 +12308,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>157283</t>
+          <t>170198</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>139902</t>
+          <t>153492</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>172448</t>
+          <t>185137</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>63,51%</t>
         </is>
       </c>
     </row>
@@ -12351,32 +12351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>50333</t>
+          <t>49247</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39450</t>
+          <t>37349</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65115</t>
+          <t>62677</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12386,32 +12386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33925</t>
+          <t>35825</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25508</t>
+          <t>28243</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42721</t>
+          <t>45356</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12421,32 +12421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>84257</t>
+          <t>85072</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70800</t>
+          <t>71217</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101702</t>
+          <t>101589</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>34,85%</t>
         </is>
       </c>
     </row>
@@ -12464,32 +12464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t>9922</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4620</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18298</t>
+          <t>17032</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12499,32 +12499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>8533</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4317</t>
+          <t>4195</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15238</t>
+          <t>14918</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12534,32 +12534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>17908</t>
+          <t>18455</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11302</t>
+          <t>11204</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27643</t>
+          <t>27640</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -12577,32 +12577,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9127</t>
+          <t>9632</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18400</t>
+          <t>18772</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12612,32 +12612,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14558</t>
+          <t>15745</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12647,32 +12647,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>16472</t>
+          <t>17769</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8804</t>
+          <t>9908</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26400</t>
+          <t>30214</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -12690,17 +12690,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>160060</t>
+          <t>166884</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>160060</t>
+          <t>166884</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>160060</t>
+          <t>166884</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12725,17 +12725,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>115860</t>
+          <t>124610</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115860</t>
+          <t>124610</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115860</t>
+          <t>124610</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12760,17 +12760,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>275920</t>
+          <t>291494</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>275920</t>
+          <t>291494</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>275920</t>
+          <t>291494</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12807,32 +12807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>263764</t>
+          <t>21204</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49112</t>
+          <t>13347</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>342316</t>
+          <t>31842</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12842,32 +12842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>9635</t>
+          <t>11767</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>6394</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17176</t>
+          <t>19674</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12877,32 +12877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>273399</t>
+          <t>32971</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62604</t>
+          <t>23139</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>378422</t>
+          <t>47603</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -12920,32 +12920,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>49267</t>
+          <t>52350</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12683</t>
+          <t>40877</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>154724</t>
+          <t>64669</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12955,32 +12955,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20257</t>
+          <t>22057</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14108</t>
+          <t>16157</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26051</t>
+          <t>28930</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12990,32 +12990,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>69524</t>
+          <t>74407</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>18131</t>
+          <t>59946</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>175626</t>
+          <t>87557</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>45,65%</t>
         </is>
       </c>
     </row>
@@ -13033,32 +13033,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>40407</t>
+          <t>44534</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10531</t>
+          <t>33546</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>127168</t>
+          <t>57077</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13068,32 +13068,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11634</t>
+          <t>12460</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7238</t>
+          <t>7206</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17220</t>
+          <t>18035</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13103,32 +13103,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>52042</t>
+          <t>56995</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14352</t>
+          <t>44722</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>133581</t>
+          <t>69956</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>36,48%</t>
         </is>
       </c>
     </row>
@@ -13146,32 +13146,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18955</t>
+          <t>24000</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>13874</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62946</t>
+          <t>36479</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13181,32 +13181,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>3412</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13216,32 +13216,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>22274</t>
+          <t>27412</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5297</t>
+          <t>17527</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60403</t>
+          <t>40581</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -13259,17 +13259,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>372394</t>
+          <t>142088</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>372394</t>
+          <t>142088</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>372394</t>
+          <t>142088</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13294,17 +13294,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>49696</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>49696</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>49696</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13329,17 +13329,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>417239</t>
+          <t>191784</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>417239</t>
+          <t>191784</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>417239</t>
+          <t>191784</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13376,32 +13376,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>35560</t>
+          <t>44253</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24559</t>
+          <t>31701</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50105</t>
+          <t>59536</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13411,27 +13411,27 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>41029</t>
+          <t>48287</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32237</t>
+          <t>37434</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53427</t>
+          <t>59732</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -13446,32 +13446,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>76589</t>
+          <t>92540</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>61765</t>
+          <t>74919</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>94787</t>
+          <t>112038</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -13489,32 +13489,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>109089</t>
+          <t>118718</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>92432</t>
+          <t>99420</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>124992</t>
+          <t>137455</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>40,93%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13524,32 +13524,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>86192</t>
+          <t>93831</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>74152</t>
+          <t>80295</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>98562</t>
+          <t>106870</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13559,32 +13559,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>195280</t>
+          <t>212549</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>174434</t>
+          <t>190698</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>216498</t>
+          <t>238118</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>46,51%</t>
         </is>
       </c>
     </row>
@@ -13602,32 +13602,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>78342</t>
+          <t>86680</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>62728</t>
+          <t>71645</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>95436</t>
+          <t>105332</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -13637,32 +13637,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>48090</t>
+          <t>54938</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>37199</t>
+          <t>43282</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>58531</t>
+          <t>66425</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13672,32 +13672,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>126432</t>
+          <t>141618</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>106908</t>
+          <t>119983</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>146560</t>
+          <t>162357</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -13715,32 +13715,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>35664</t>
+          <t>40423</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24264</t>
+          <t>27606</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52582</t>
+          <t>55706</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13750,32 +13750,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>23217</t>
+          <t>24873</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16790</t>
+          <t>17401</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32895</t>
+          <t>33385</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13785,32 +13785,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>58881</t>
+          <t>65296</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44647</t>
+          <t>50326</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75595</t>
+          <t>82675</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -13828,17 +13828,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>258655</t>
+          <t>290074</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>258655</t>
+          <t>290074</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>258655</t>
+          <t>290074</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13863,17 +13863,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>198527</t>
+          <t>221928</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>198527</t>
+          <t>221928</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>198527</t>
+          <t>221928</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13898,17 +13898,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>457182</t>
+          <t>512002</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>457182</t>
+          <t>512002</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>457182</t>
+          <t>512002</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13945,32 +13945,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>16727</t>
+          <t>20272</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9367</t>
+          <t>11929</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27652</t>
+          <t>30765</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13980,32 +13980,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>16414</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>12193</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24661</t>
+          <t>26840</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14015,32 +14015,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>33140</t>
+          <t>38881</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21788</t>
+          <t>27546</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>45921</t>
+          <t>50741</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -14058,32 +14058,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>30468</t>
+          <t>32011</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>20348</t>
+          <t>21438</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45463</t>
+          <t>43549</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14093,32 +14093,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>36195</t>
+          <t>43727</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18767</t>
+          <t>35437</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>48712</t>
+          <t>53633</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14128,32 +14128,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>66663</t>
+          <t>75738</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>44354</t>
+          <t>60343</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>84261</t>
+          <t>91786</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,38%</t>
         </is>
       </c>
     </row>
@@ -14171,32 +14171,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>44565</t>
+          <t>59889</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>32911</t>
+          <t>45451</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>56716</t>
+          <t>74986</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14206,32 +14206,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>49228</t>
+          <t>56847</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>26475</t>
+          <t>45528</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>65629</t>
+          <t>66899</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14241,32 +14241,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>93792</t>
+          <t>116735</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>64712</t>
+          <t>99934</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>113229</t>
+          <t>135602</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>41,93%</t>
         </is>
       </c>
     </row>
@@ -14284,32 +14284,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>40514</t>
+          <t>56578</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>28855</t>
+          <t>44492</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>53851</t>
+          <t>73650</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -14319,32 +14319,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>61013</t>
+          <t>35437</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>32257</t>
+          <t>27109</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>105381</t>
+          <t>46654</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -14354,32 +14354,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>101527</t>
+          <t>92015</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>71559</t>
+          <t>73965</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>163467</t>
+          <t>111622</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>34,52%</t>
         </is>
       </c>
     </row>
@@ -14397,17 +14397,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>132274</t>
+          <t>168750</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>132274</t>
+          <t>168750</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>132274</t>
+          <t>168750</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14432,17 +14432,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>162849</t>
+          <t>154620</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>162849</t>
+          <t>154620</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>162849</t>
+          <t>154620</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14467,17 +14467,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>295123</t>
+          <t>323369</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>295123</t>
+          <t>323369</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>295123</t>
+          <t>323369</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14514,32 +14514,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>515499</t>
+          <t>305259</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>333074</t>
+          <t>274532</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>792869</t>
+          <t>338514</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14549,32 +14549,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>205746</t>
+          <t>228219</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>169972</t>
+          <t>207729</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>230470</t>
+          <t>251582</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14584,32 +14584,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>721245</t>
+          <t>533479</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>537783</t>
+          <t>494033</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1139850</t>
+          <t>572030</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -14627,32 +14627,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>289935</t>
+          <t>306455</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>154900</t>
+          <t>272871</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>386585</t>
+          <t>339387</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14662,32 +14662,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>227211</t>
+          <t>249192</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>185087</t>
+          <t>230167</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>250917</t>
+          <t>272231</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14697,32 +14697,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>517145</t>
+          <t>555647</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>311345</t>
+          <t>518503</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>616611</t>
+          <t>595995</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>35,48%</t>
         </is>
       </c>
     </row>
@@ -14740,32 +14740,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>185738</t>
+          <t>215256</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>91902</t>
+          <t>187907</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>250587</t>
+          <t>243283</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14775,32 +14775,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>136594</t>
+          <t>153960</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>114937</t>
+          <t>134192</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>158003</t>
+          <t>174060</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14810,32 +14810,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>322331</t>
+          <t>369216</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>199381</t>
+          <t>332355</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>384819</t>
+          <t>404793</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -14853,32 +14853,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>112069</t>
+          <t>140792</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>55175</t>
+          <t>115912</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>155662</t>
+          <t>171146</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14888,32 +14888,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>103149</t>
+          <t>80492</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>68675</t>
+          <t>65945</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>216778</t>
+          <t>97162</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14923,32 +14923,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>215218</t>
+          <t>221284</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>145228</t>
+          <t>191112</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>305407</t>
+          <t>253966</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -14966,17 +14966,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1103241</t>
+          <t>967763</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1103241</t>
+          <t>967763</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1103241</t>
+          <t>967763</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -15001,17 +15001,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>672699</t>
+          <t>711862</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>672699</t>
+          <t>711862</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>672699</t>
+          <t>711862</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15036,17 +15036,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1775939</t>
+          <t>1679625</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1775939</t>
+          <t>1679625</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1775939</t>
+          <t>1679625</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
